--- a/output/pdf_financials_xlsx/SKE.xlsx
+++ b/output/pdf_financials_xlsx/SKE.xlsx
@@ -1420,10 +1420,10 @@
         <v>0.644</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0</v>
+        <v>-303.878</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>3.462</v>
+        <v>-362.22</v>
       </c>
     </row>
     <row r="18">
@@ -1666,10 +1666,10 @@
         <v>-108.98</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>151.939</v>
+        <v>-151.939</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>182.841</v>
+        <v>-182.841</v>
       </c>
     </row>
     <row r="21">
@@ -1852,10 +1852,10 @@
         <v>-108.98</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>151.939</v>
+        <v>-151.939</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>182.841</v>
+        <v>-182.841</v>
       </c>
     </row>
     <row r="24">
@@ -2086,10 +2086,10 @@
         <v>84.48062</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-99.30653599999999</v>
+        <v>99.30653599999999</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-114.99434</v>
+        <v>114.99434</v>
       </c>
     </row>
     <row r="27">
@@ -2426,10 +2426,10 @@
         <v>-0.5874625994307815</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>1.929991805060793</v>
+        <v>201.9299918050608</v>
       </c>
     </row>
     <row r="32">
@@ -6064,49 +6064,49 @@
         <v>3.02573</v>
       </c>
       <c r="D92" s="3" t="n">
+        <v>3.02573</v>
+      </c>
+      <c r="E92" s="3" t="n">
         <v>3.62076</v>
       </c>
-      <c r="E92" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.633238</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.633238</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.425536</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.417877</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>8.61032</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>9.299442000000001</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>11.080018</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>13.585108</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>40.608</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>39.879</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>48.299</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>47.346</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>66.029</v>
       </c>
     </row>
     <row r="93">
@@ -7651,16 +7651,16 @@
         <v>0</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.475</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.379</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-14.354</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>-0.857</v>
+        <v>-9.656000000000001</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>-3.216</v>
@@ -11106,7 +11106,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -15779,7 +15783,11 @@
           <t>Reserves 17</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -16979,7 +16987,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -17585,7 +17597,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -18183,7 +18199,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -19080,7 +19100,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -19781,7 +19805,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -20672,7 +20700,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -21692,7 +21724,11 @@
           <t>Reserves (Note 10) 3,633,238</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -22908,7 +22944,11 @@
           <t>Reserves (Note 9) 3,633,238</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -26886,7 +26926,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -33814,7 +33858,11 @@
           <t>Exploration and evaluation asset expenditures 10</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -48388,10 +48436,10 @@
         </is>
       </c>
       <c r="T398" s="5" t="n">
-        <v>151.939</v>
+        <v>-151.939</v>
       </c>
       <c r="U398" s="5" t="n">
-        <v>182.841</v>
+        <v>-182.841</v>
       </c>
     </row>
     <row r="399">

--- a/output/pdf_financials_xlsx/SKE.xlsx
+++ b/output/pdf_financials_xlsx/SKE.xlsx
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.015005</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000213</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001611</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1080,40 +1080,40 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000144</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-4e-06</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015493</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.025757</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.025006</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.021158</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.07022299999999999</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.228</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.361</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-3.694</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-3.065</v>
       </c>
     </row>
     <row r="13">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.415569</v>
+        <v>-6.430574</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.46453</v>
+        <v>-6.464743</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.756918</v>
+        <v>-0.758529</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2118,40 +2118,40 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.191363</v>
+        <v>-0.191507</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.12376</v>
+        <v>-3.123756</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-7.070154</v>
+        <v>-7.054661</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-13.551479</v>
+        <v>-13.525722</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-10.002067</v>
+        <v>-9.977061000000001</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-15.520022</v>
+        <v>-15.498864</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-27.082863</v>
+        <v>-27.01264</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-117.567</v>
+        <v>-117.339</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-88.89</v>
+        <v>-88.529</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-109.624</v>
+        <v>-107.584</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>151.939</v>
+        <v>155.633</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>179.379</v>
+        <v>182.444</v>
       </c>
     </row>
     <row r="28">
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.415569</v>
+        <v>-6.430574</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.46453</v>
+        <v>-6.464743</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.756918</v>
+        <v>-0.758529</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2242,40 +2242,40 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.191363</v>
+        <v>-0.191507</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.12376</v>
+        <v>-3.123756</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-7.070154</v>
+        <v>-7.054661</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-13.551479</v>
+        <v>-13.525722</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-10.002067</v>
+        <v>-9.977061000000001</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-15.520022</v>
+        <v>-15.498864</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-27.082863</v>
+        <v>-27.01264</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-115.552</v>
+        <v>-115.324</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-86.97799999999999</v>
+        <v>-86.617</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-107.224</v>
+        <v>-105.184</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>160.162</v>
+        <v>163.856</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>180.623</v>
+        <v>183.688</v>
       </c>
     </row>
     <row r="30">
@@ -2538,22 +2538,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.048277</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.006332</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.006332</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.137317</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.032216</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.02469</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>1.102073</v>
@@ -2654,22 +2654,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.007</v>
+        <v>0.055277</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.008224</v>
+        <v>0.014556</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.008224</v>
+        <v>0.014556</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.005775</v>
+        <v>0.143092</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.000413</v>
+        <v>0.032629</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.02469</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>1.102073</v>
@@ -3350,22 +3350,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.074056</v>
+        <v>0.025779</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.013427</v>
+        <v>0.007095</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.232223</v>
+        <v>0.225891</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.158006</v>
+        <v>0.020689</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.040568</v>
+        <v>0.008352</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.034518</v>
+        <v>0.009828</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.03477</v>
@@ -8020,22 +8020,22 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.3075</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-1.573</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.477</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.991</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-8.582000000000001</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-12.111</v>
       </c>
     </row>
     <row r="125">
@@ -8082,22 +8082,22 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.3075</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-1.573</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.477</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.991</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-8.582000000000001</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-12.111</v>
       </c>
     </row>
     <row r="126">
@@ -19908,7 +19908,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -22027,7 +22027,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -27413,7 +27413,11 @@
           <t>Lease payments 10</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -31268,7 +31272,11 @@
           <t>Lease payments 12</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -34963,7 +34971,11 @@
           <t>Lease payments 14</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -37874,7 +37886,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -39870,7 +39886,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -47852,7 +47872,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -51890,7 +51910,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -55579,7 +55599,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -61269,7 +61289,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -69265,7 +69285,7 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
@@ -74416,7 +74436,7 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E659" s="5" t="n">
